--- a/ig/DM-JANVIER-2026/ValueSet-jdv-j386-type-enseignement-specialise-ms.xlsx
+++ b/ig/DM-JANVIER-2026/ValueSet-jdv-j386-type-enseignement-specialise-ms.xlsx
@@ -114,7 +114,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/r408-type-enseignement-specialise</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r408-type-enseignement-specialise</t>
   </si>
 </sst>
 </file>

--- a/ig/DM-JANVIER-2026/ValueSet-jdv-j386-type-enseignement-specialise-ms.xlsx
+++ b/ig/DM-JANVIER-2026/ValueSet-jdv-j386-type-enseignement-specialise-ms.xlsx
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Niveau ou situation scolaire de l'usager.</t>
+    <t>Type d'enseignement spécialisé.</t>
   </si>
   <si>
     <t>Purpose</t>
